--- a/examples/sixdrive12resp/results/sdynpy_frame6x12_profile.xlsx
+++ b/examples/sixdrive12resp/results/sdynpy_frame6x12_profile.xlsx
@@ -2,8 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-67180" yWindow="1540" windowWidth="34560" windowHeight="21680" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Channel Table" sheetId="1" state="visible" r:id="rId1"/>
@@ -12,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Profile" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -48,12 +49,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -417,7 +417,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:X20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="inlineStr">
@@ -1126,7 +1126,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -1135,11 +1135,11 @@
         </is>
       </c>
       <c r="B1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Hardware Indices: 0 - NI DAQmx; 1 - LAN XI; 2 - Data Physics Quattro; 3 - Data Physics 900 Series; 4 - Exodus Modal Solution; 5 - State Space Integration; 6 - SDynPy System Integration</t>
+          <t>Hardware Indices: 0 - NI DAQmx; 1 - LAN XI; 2 - Data Physics Quattro; 3 - Data Physics 900 Series; 4 - Exodus Modal Solution; 5 - State Space Integration; 6 - SDynPy System Integration; 7 - SDynPy Nonlinear System Integration</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>/Users/nhunterjr/Documents/Code/python/rattlesnake-vibration-controller/examples/sixdrive12resp/results/sdynpy_frame6x12_system_nonlinear_allmodes.npz</t>
+          <t>/Users/nhunterjr/Documents/Code/python/rattlesnake-vibration-controller/examples/sixdrive12resp/results/sdynpy_frame6x12_system.npz</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5120</v>
+        <v>4096</v>
       </c>
     </row>
     <row r="4">
@@ -1216,12 +1216,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
-  <cols>
-    <col width="22.33203125" customWidth="1" style="1" min="1" max="1"/>
-    <col width="20.5" customWidth="1" style="1" min="2" max="2"/>
-  </cols>
+  <dimension ref="A1:Z30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -1234,6 +1230,16 @@
           <t>Random</t>
         </is>
       </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>Control Averaging Type:</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>Exponential</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1242,7 +1248,15 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5120</v>
+        <v>4096</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Control Averaging Coefficient:</t>
+        </is>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.05</v>
       </c>
     </row>
     <row r="3">
@@ -1252,7 +1266,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -1306,7 +1320,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -1351,7 +1365,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>/Users/nhunterjr/Documents/Code/python/rattlesnake-vibration-controller/control_laws/octave_band_switching_control.py</t>
+          <t>/Users/nhunterjr/Documents/Code/python/rattlesnake-vibration-controller/control_laws/control_laws.py</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1377,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>octave_band_switching_control</t>
+          <t>match_trace_pseudoinverse_pi</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1389,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1e-6,0.05,20,1.0,0.95,1.0,0.0,6</t>
+          <t>1e-15,0.95,-12,0.2,0.8,1.0,8</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1453,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -1586,7 +1600,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
